--- a/data/trans_bre/P12_3_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,14</t>
+          <t>-0,5; 4,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,8</t>
+          <t>2,52; 9,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,73</t>
+          <t>0,74; 7,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,6</t>
+          <t>-0,26; 5,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 136,07</t>
+          <t>-11,82; 143,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 126,53</t>
+          <t>24,46; 130,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 97,4</t>
+          <t>5,25; 98,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 72,22</t>
+          <t>-2,63; 71,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,21</t>
+          <t>0,47; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,14</t>
+          <t>2,82; 8,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,06</t>
+          <t>1,32; 6,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,77</t>
+          <t>3,72; 12,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 112,07</t>
+          <t>5,92; 104,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,69; 118,02</t>
+          <t>28,0; 120,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 129,44</t>
+          <t>19,71; 138,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 267,38</t>
+          <t>31,58; 273,22</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,98</t>
+          <t>-0,12; 5,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,79</t>
+          <t>1,41; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,95</t>
+          <t>1,05; 7,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 2,36</t>
+          <t>-8,48; 1,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 122,93</t>
+          <t>-4,85; 144,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,86; 138,52</t>
+          <t>16,5; 135,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 128,28</t>
+          <t>10,26; 130,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 24,86</t>
+          <t>-59,91; 19,3</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,15</t>
+          <t>3,4; 8,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,84</t>
+          <t>2,14; 8,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,96</t>
+          <t>2,52; 8,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,62</t>
+          <t>0,09; 6,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,0; 201,74</t>
+          <t>54,45; 197,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 104,04</t>
+          <t>19,66; 108,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,63; 117,65</t>
+          <t>27,62; 117,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 64,71</t>
+          <t>0,34; 67,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,66</t>
+          <t>2,2; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,67</t>
+          <t>3,58; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,9</t>
+          <t>2,9; 5,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,62</t>
+          <t>0,64; 5,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,51; 103,14</t>
+          <t>38,81; 104,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,33; 88,46</t>
+          <t>40,88; 90,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,41; 85,18</t>
+          <t>35,64; 85,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 69,49</t>
+          <t>7,71; 65,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_3_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,21</t>
+          <t>-0,47; 4,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,1</t>
+          <t>2,07; 9,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,98</t>
+          <t>0,76; 7,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,62</t>
+          <t>-0,2; 5,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 143,12</t>
+          <t>-10,42; 136,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,46; 130,75</t>
+          <t>22,78; 136,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 98,57</t>
+          <t>6,24; 100,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 71,68</t>
+          <t>-2,42; 70,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,23</t>
+          <t>0,49; 5,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,48</t>
+          <t>2,65; 8,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,23</t>
+          <t>1,22; 6,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,0</t>
+          <t>3,42; 8,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 104,91</t>
+          <t>6,06; 108,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 120,36</t>
+          <t>26,92; 122,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 138,93</t>
+          <t>18,65; 132,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,58; 273,22</t>
+          <t>32,52; 111,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,16%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,35</t>
+          <t>-0,11; 5,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,64</t>
+          <t>1,77; 8,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,37</t>
+          <t>1,12; 7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 1,93</t>
+          <t>-1,79; 4,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 144,31</t>
+          <t>-3,6; 125,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 135,04</t>
+          <t>19,31; 143,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 130,65</t>
+          <t>10,6; 128,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 19,3</t>
+          <t>-13,97; 56,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,0</t>
+          <t>3,37; 8,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,16</t>
+          <t>2,27; 7,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,05</t>
+          <t>2,71; 8,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,88</t>
+          <t>1,78; 7,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,45; 197,52</t>
+          <t>55,02; 201,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 108,83</t>
+          <t>21,74; 107,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,62; 117,22</t>
+          <t>27,04; 119,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 67,33</t>
+          <t>11,8; 68,93</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,7</t>
+          <t>2,29; 4,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,77</t>
+          <t>3,67; 6,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,75</t>
+          <t>2,86; 5,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,47</t>
+          <t>2,66; 5,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,81; 104,09</t>
+          <t>41,28; 107,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,88; 90,04</t>
+          <t>42,26; 92,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,64; 85,26</t>
+          <t>34,84; 86,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 65,24</t>
+          <t>23,3; 57,53</t>
         </is>
       </c>
     </row>
